--- a/test/data/mps155_timezone_bug_v17_validated.xlsx
+++ b/test/data/mps155_timezone_bug_v17_validated.xlsx
@@ -1496,6 +1496,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve"> X</t>
+  </si>
+  <si>
     <r>
       <rPr/>
       <t xml:space="preserve">Konsiliarlabor für </t>
@@ -1575,6 +1578,9 @@
       </rPr>
       <t xml:space="preserve"> spp.</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">test@test.de</t>
   </si>
   <si>
     <r>
@@ -6676,13 +6682,13 @@
       <c r="N14" s="179"/>
       <c r="O14" s="180"/>
       <c r="P14" t="s" s="83">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="Q14" s="63"/>
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
       <c r="W14" t="s" s="43">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:23" s="42" customFormat="1" ht="17.100000000000001" customHeight="1">
@@ -6714,7 +6720,7 @@
       <c r="R15" s="63"/>
       <c r="S15" s="63"/>
       <c r="W15" t="s" s="44">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:23" s="42" customFormat="1" ht="17.100000000000001" customHeight="1">
@@ -6728,7 +6734,7 @@
       <c r="H16" s="198"/>
       <c r="I16" s="73"/>
       <c r="J16" t="s" s="178">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K16" s="179"/>
       <c r="L16" s="179"/>
@@ -6742,7 +6748,7 @@
       <c r="R16" s="63"/>
       <c r="S16" s="63"/>
       <c r="W16" t="s" s="43">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:23" s="42" customFormat="1" ht="17.100000000000001" customHeight="1">
@@ -6794,7 +6800,7 @@
       <c r="N18" s="182"/>
       <c r="O18" s="183"/>
       <c r="P18" t="s" s="83">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="Q18" s="63"/>
       <c r="R18" s="63"/>
@@ -6895,7 +6901,7 @@
       </c>
       <c r="B22" s="222"/>
       <c r="C22" t="s" s="198">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="D22" s="198"/>
       <c r="E22" s="198"/>
@@ -6904,7 +6910,7 @@
       <c r="H22" s="198"/>
       <c r="I22" s="73"/>
       <c r="J22" t="s" s="178">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K22" s="179"/>
       <c r="L22" s="179"/>
@@ -7343,10 +7349,10 @@
         <v>102</v>
       </c>
       <c r="D41" t="s" s="29">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E41" t="s" s="30">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F41" t="s" s="29">
         <v>28</v>
@@ -7355,46 +7361,46 @@
         <v>0</v>
       </c>
       <c r="H41" t="s" s="29">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I41" t="s" s="32">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J41" t="s" s="30">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K41" t="s" s="29">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L41" t="s" s="32">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M41" t="s" s="31">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N41" t="s" s="30">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O41" t="s" s="29">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P41" t="s" s="32">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q41" t="s" s="30">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="R41" t="s" s="29">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="S41" t="s" s="30">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="T41" t="s" s="33">
         <v>31</v>
       </c>
       <c r="U41" t="s" s="33">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V41" t="s" s="33">
         <v>150</v>
@@ -7402,61 +7408,61 @@
     </row>
     <row r="42" spans="1:26" s="23" customFormat="1" ht="12.75">
       <c r="A42" t="s" s="262">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s" s="263">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C42" t="s" s="264">
         <v>161</v>
       </c>
       <c r="D42" t="s" s="265">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E42" t="s" s="266">
         <v>161</v>
       </c>
       <c r="F42" t="s" s="267">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G42" t="s" s="268">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H42" t="s" s="269">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I42" t="s" s="270">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J42" t="s" s="271">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K42" t="s" s="272">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L42" t="s" s="273">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M42" t="s" s="274">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N42" t="s" s="275">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O42" t="s" s="276">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P42" t="s" s="277">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q42" t="s" s="278">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="R42" t="s" s="279">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="S42" t="s" s="280">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="T42" t="s" s="281">
         <v>161</v>
@@ -7471,61 +7477,61 @@
     </row>
     <row r="43" spans="1:26" s="6" customFormat="1" ht="12.75">
       <c r="A43" t="s" s="285">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B43" t="s" s="286">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C43" t="s" s="287">
         <v>161</v>
       </c>
       <c r="D43" t="s" s="288">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E43" t="s" s="289">
         <v>161</v>
       </c>
       <c r="F43" t="s" s="290">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G43" t="s" s="291">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H43" t="s" s="292">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I43" t="s" s="293">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J43" t="s" s="294">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K43" t="s" s="295">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L43" t="s" s="296">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M43" t="s" s="297">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N43" t="s" s="298">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O43" t="s" s="299">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P43" t="s" s="300">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q43" t="s" s="301">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="R43" t="s" s="302">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="S43" t="s" s="303">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="T43" t="s" s="304">
         <v>161</v>
@@ -48801,7 +48807,7 @@
         <v>69</v>
       </c>
       <c r="B8" t="s" s="133">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C8" t="s" s="134">
         <v>120</v>
@@ -48839,7 +48845,7 @@
         <v>70</v>
       </c>
       <c r="B9" t="s" s="105">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C9" t="s" s="140">
         <v>98</v>
@@ -48947,14 +48953,14 @@
         <v>75</v>
       </c>
       <c r="B12" t="s" s="133">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C12" t="s" s="134">
         <v>121</v>
       </c>
       <c r="D12" s="244"/>
       <c r="E12" t="s" s="239">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F12" s="99"/>
       <c r="G12" s="95"/>
@@ -48983,7 +48989,7 @@
         <v>77</v>
       </c>
       <c r="B13" t="s" s="96">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C13" t="s" s="98">
         <v>76</v>
@@ -49017,7 +49023,7 @@
         <v>79</v>
       </c>
       <c r="B14" t="s" s="105">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C14" t="s" s="140">
         <v>78</v>
@@ -49051,7 +49057,7 @@
         <v>80</v>
       </c>
       <c r="B15" t="s" s="133">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C15" t="s" s="134">
         <v>122</v>
@@ -49089,7 +49095,7 @@
         <v>81</v>
       </c>
       <c r="B16" t="s" s="96">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C16" t="s" s="98">
         <v>123</v>
@@ -49123,7 +49129,7 @@
         <v>82</v>
       </c>
       <c r="B17" t="s" s="96">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s" s="98">
         <v>149</v>
@@ -49157,7 +49163,7 @@
         <v>84</v>
       </c>
       <c r="B18" t="s" s="105">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C18" t="s" s="140">
         <v>124</v>
@@ -49191,7 +49197,7 @@
         <v>85</v>
       </c>
       <c r="B19" t="s" s="133">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C19" t="s" s="134">
         <v>125</v>
@@ -49227,7 +49233,7 @@
         <v>86</v>
       </c>
       <c r="B20" t="s" s="96">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s" s="98">
         <v>126</v>
@@ -49261,7 +49267,7 @@
         <v>87</v>
       </c>
       <c r="B21" t="s" s="105">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C21" t="s" s="140">
         <v>152</v>
@@ -49297,7 +49303,7 @@
         <v>88</v>
       </c>
       <c r="B22" t="s" s="133">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C22" t="s" s="134">
         <v>128</v>
@@ -49331,14 +49337,14 @@
         <v>89</v>
       </c>
       <c r="B23" t="s" s="105">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C23" t="s" s="140">
         <v>127</v>
       </c>
       <c r="D23" s="141"/>
       <c r="E23" t="s" s="142">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F23" s="99"/>
       <c r="G23" s="95"/>
@@ -49401,7 +49407,7 @@
         <v>135</v>
       </c>
       <c r="B25" t="s" s="148">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C25" t="s" s="149">
         <v>137</v>
@@ -49440,7 +49446,7 @@
         <v>150</v>
       </c>
       <c r="C26" t="s" s="106">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D26" s="107"/>
       <c r="E26" s="108"/>
@@ -49641,7 +49647,7 @@
     </row>
     <row r="33" spans="1:26" s="94" customFormat="1" ht="26.1" customHeight="1">
       <c r="A33" t="s" s="249">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B33" s="250"/>
       <c r="C33" s="250"/>
@@ -49699,7 +49705,7 @@
     </row>
     <row r="35" spans="1:26" s="94" customFormat="1" ht="51.95" customHeight="1">
       <c r="A35" t="s" s="233">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B35" s="234"/>
       <c r="C35" s="234"/>
@@ -49729,7 +49735,7 @@
     </row>
     <row r="36" spans="1:26" s="94" customFormat="1" ht="52.5" customHeight="1">
       <c r="A36" t="s" s="236">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B36" s="237"/>
       <c r="C36" s="237"/>
@@ -49849,7 +49855,7 @@
     </row>
     <row r="40" spans="1:26" s="94" customFormat="1" ht="26.1" customHeight="1">
       <c r="A40" t="s" s="236">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B40" s="237"/>
       <c r="C40" s="237"/>
